--- a/docs/modules/bsee/data/SME_Roy_attachments/2025-08-01/drilling_and_completion_days_by_api.xlsx
+++ b/docs/modules/bsee/data/SME_Roy_attachments/2025-08-01/drilling_and_completion_days_by_api.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07f9c9cfd5dcd705/Roy/FDAS/Mktg/1-World Oil/2025 article/July/eWellWARRawData/eWellWARRawData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sk Samdan\Desktop\github\worldenergydata\docs\modules\bsee\data\SME_Roy_attachments\2025-08-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_011560E1214B8F081B2C4C77C56A2ACD797950E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4B5AD4A-78BD-48CE-A349-F4FDA9CB4B30}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF8E44D-D04E-4D40-AC12-86322C3F6994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1774,7 +1772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L123"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -6451,22 +6449,6 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H127">
-        <f>SUM(H2:H126)</f>
-        <v>9787</v>
-      </c>
-      <c r="I127">
-        <f>SUM(I2:I126)</f>
-        <v>5801</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="I128">
-        <f>H127+I127</f>
-        <v>15588</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
